--- a/TASK2/Scenariji/SC04_OtkazivanjeRezervacije.xlsx
+++ b/TASK2/Scenariji/SC04_OtkazivanjeRezervacije.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan otkazuje prethodno kreiranu rezervaciju grupnog treninga.</t>
+          <t>Član otkazuje prethodno kreiranu rezervaciju grupnog treninga.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Otkazivanje rezervacije najkasnije 2 sata prije pocetka</t>
+          <t>Otkazivanje rezervacije najkasnije 2 sata prije početka</t>
         </is>
       </c>
     </row>
@@ -497,14 +497,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clan je prijavljen. Clan ima aktivnu rezervaciju. Do pocetka treninga je vise od 2 sata.</t>
+          <t>Član je prijavljen. Član ima aktivnu rezervaciju. Do početka treninga je više od 2 sata.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -516,12 +516,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Otkazivanje nije moguce jer je do pocetka manje od 2 sata.</t>
+          <t>Otkazivanje nije moguće jer je do početka manje od 2 sata.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan pregledava rezervacije, bira rezervaciju za otkazivanje, sistem brise rezervaciju.</t>
+          <t>Član pregledava rezervacije, bira rezervaciju za otkazivanje, sistem briše rezervaciju.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Manje od 2 sata do pocetka treninga</t>
-        </is>
-      </c>
-    </row>
+          <t>Manje od 2 sata do početka treninga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,7 +584,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -630,7 +631,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Provjera da li je do pocetka treninga vise od 2 sata</t>
+          <t>6. Provjera da li je do početka treninga više od 2 sata</t>
         </is>
       </c>
     </row>
@@ -644,7 +645,7 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8. Azuriranje broja slobodnih mjesta na treningu</t>
+          <t>8. Ažuriranje broja slobodnih mjesta na treningu</t>
         </is>
       </c>
     </row>
@@ -655,17 +656,18 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Manje od 2 sata do pocetka</t>
+          <t>Alternativni Tok - Manje od 2 sata do početka</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -677,28 +679,28 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>6a. Sistem detektuje da je do pocetka manje od 2 sata</t>
+          <t>6a. Sistem detektuje da je do početka manje od 2 sata</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>6b. Prikaz poruke da otkazivanje nije moguce</t>
+          <t>6b. Prikaz poruke da otkazivanje nije moguće</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>6c. Clan potvrduje primanje poruke</t>
+          <t>6c. Član potvrđuje primanje poruke</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>6d. Sistem vraca clana na listu rezervacija</t>
+          <t>6d. Sistem vraća člana na listu rezervacija</t>
         </is>
       </c>
     </row>
